--- a/Verificacion_citas_Cap_V.xlsx
+++ b/Verificacion_citas_Cap_V.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -638,7 +638,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>(1) SUP-JIN-194/2025: el proyecto de Rodríguez Mondragón reproducido en su voto y las pp. 43-252 del voto están en el tramo del PDF «compressed-1-300» (7.7 MB), cuya descarga agota la sesión de Drive; las notas que remiten a ese tramo quedan pendientes. (2) Ferrer, Prueba sin convicción: el tramo impreso pp. 139-148 no está paginado en las copias descargables; las notas de ese tramo se localizaron por contenido (±1 página).</t>
+          <t>Ferrer, Prueba sin convicción: el tramo impreso pp. 139-148 no está paginado en las copias descargables; las notas de ese tramo se localizaron por contenido (±1 página). El SUP-JIN-194/2025 (voto y proyecto) se cotejó con el PDF en tramos.</t>
         </is>
       </c>
     </row>
@@ -3070,17 +3070,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF no descargable.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 129 y nota 80 (Tesis XXXVII/2004), p. 100.</t>
         </is>
       </c>
       <c r="J52" s="7" t="n"/>
@@ -3760,17 +3760,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF no descargable.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 127, pp. 100-101.</t>
         </is>
       </c>
       <c r="J67" s="7" t="n"/>
@@ -3925,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4009,56 +4009,6 @@
       <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Nota: «párrafo tercero» → «párrafo cuarto».</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="n">
-        <v>711</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de sentencia presentado por el magistrado Reyes Rodríguez Mondragón en el SUP-JIN-194/2025 y acumulados, reproducido en su voto particular, párrafo 129 y nota 80, p. 100 del voto, donde cita la tesis XXXVII/2004, PRUEBAS INDIRECTAS. SON IDÓNEAS PARA ACREDITAR ACTIVIDADES ILÍCITAS REALIZADAS POR LOS PARTIDOS POLÍTICOS.</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF no descargable.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>726</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 127, pp. 100 y 101 del voto.</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF no descargable.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4210,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fuentes citadas (SUP-JIN-194/2025, párrs. 55-56; Gascón; Ferrer)</t>
+          <t>SUP-JIN-194/2025, párrs. 55-56; Gascón; Ferrer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
